--- a/input/PL/parameters.xlsx
+++ b/input/PL/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_JAN/input/PL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_APR/input/PL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468A27D1-6BDB-7E4F-92C4-2A4F66811887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1881DF-B6E8-2D4D-919A-D17868ABF2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24900" yWindow="2780" windowWidth="20300" windowHeight="19580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22020" yWindow="4520" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -945,7 +945,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -977,7 +977,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="10">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -985,7 +985,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="10">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">

--- a/input/PL/parameters.xlsx
+++ b/input/PL/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_APR/input/PL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1881DF-B6E8-2D4D-919A-D17868ABF2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1DF77-E497-7B46-AFCC-8E3518BC62E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22020" yWindow="4520" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22020" yWindow="3940" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -977,7 +977,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="10">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -985,7 +985,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="10">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">

--- a/input/PL/parameters.xlsx
+++ b/input/PL/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_APR/input/PL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1DF77-E497-7B46-AFCC-8E3518BC62E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8817CC-DB37-6A4D-908C-98875C54EC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22020" yWindow="3940" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -977,7 +977,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="10">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -985,7 +985,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="10">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">

--- a/input/PL/parameters.xlsx
+++ b/input/PL/parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_APR/input/PL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8817CC-DB37-6A4D-908C-98875C54EC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC85DE7-66D8-F144-8C4C-BBDE8169FA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22020" yWindow="3940" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="1">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">

--- a/input/PL/parameters.xlsx
+++ b/input/PL/parameters.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_APR/input/PL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\_IAB\Projekte\SimPathsEU\input\PL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8817CC-DB37-6A4D-908C-98875C54EC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716CBFA3-64BD-4C1C-9B53-0E9CC9A5EBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22020" yWindow="3940" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -297,7 +302,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,7 +380,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -678,13 +683,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.84375" defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="42.3046875" customWidth="1"/>
+    <col min="2" max="2" width="25.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -692,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -700,7 +705,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -708,7 +713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -716,7 +721,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -724,7 +729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -732,7 +737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -740,7 +745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -748,7 +753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -756,7 +761,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -764,7 +769,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -772,7 +777,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -780,7 +785,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -788,7 +793,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -796,7 +801,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -804,7 +809,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -812,7 +817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -820,7 +825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -828,7 +833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -836,7 +841,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -844,7 +849,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -852,7 +857,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
@@ -860,7 +865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -868,15 +873,15 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -884,7 +889,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
@@ -892,7 +897,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
@@ -900,7 +905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -908,7 +913,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
@@ -916,7 +921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -924,7 +929,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
@@ -932,7 +937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -940,7 +945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -948,7 +953,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
@@ -956,7 +961,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
@@ -964,7 +969,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="15.9">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -972,7 +977,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="15.9">
       <c r="A37" s="9" t="s">
         <v>80</v>
       </c>
@@ -980,7 +985,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="15.9">
       <c r="A38" s="9" t="s">
         <v>81</v>
       </c>
@@ -988,7 +993,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="15.9">
       <c r="A39" s="9" t="s">
         <v>82</v>
       </c>
@@ -996,7 +1001,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15.9">
       <c r="A40" s="9" t="s">
         <v>83</v>
       </c>
@@ -1013,22 +1018,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED917CC-650D-7949-BB93-913B978B4F4C}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="57.5" customWidth="1"/>
-    <col min="2" max="2" width="93.33203125" customWidth="1"/>
+    <col min="1" max="1" width="57.4609375" customWidth="1"/>
+    <col min="2" max="2" width="93.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.9">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="15.9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="15.9">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -1036,7 +1041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15.9">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -1044,7 +1049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15.9">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1052,7 +1057,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="15.9">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1060,7 +1065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15.9">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1068,7 +1073,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15.9">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1076,7 +1081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15.9">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15.9">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1092,7 +1097,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15.9">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1100,7 +1105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15.9">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1108,7 +1113,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="15.9">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1116,7 +1121,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="15.9">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -1124,7 +1129,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15.9">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -1132,7 +1137,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="15.9">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -1140,7 +1145,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.9">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -1148,7 +1153,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.9">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -1156,7 +1161,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15.9">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -1164,7 +1169,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15.9">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -1172,7 +1177,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.9">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -1180,7 +1185,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="15.9">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -1188,7 +1193,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="15.9">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
@@ -1196,7 +1201,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="15.9">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -1204,7 +1209,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="15.9">
       <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
@@ -1212,7 +1217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="15.9">
       <c r="A26" s="4" t="s">
         <v>27</v>
       </c>
@@ -1220,7 +1225,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="15.9">
       <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="15.9">
       <c r="A28" s="4" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1241,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="15.9">
       <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
@@ -1244,7 +1249,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="15.9">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -1252,7 +1257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="15.9">
       <c r="A31" s="4" t="s">
         <v>32</v>
       </c>
@@ -1260,7 +1265,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="15.9">
       <c r="A32" s="4" t="s">
         <v>33</v>
       </c>
@@ -1268,7 +1273,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.9">
       <c r="A33" s="4" t="s">
         <v>34</v>
       </c>
@@ -1276,7 +1281,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="15.9">
       <c r="A34" s="4" t="s">
         <v>35</v>
       </c>
@@ -1284,7 +1289,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="15.9">
       <c r="A35" s="4" t="s">
         <v>36</v>
       </c>
@@ -1292,7 +1297,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="15.9">
       <c r="A36" s="4" t="s">
         <v>37</v>
       </c>
@@ -1300,7 +1305,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15.9">
       <c r="A37" s="4" t="s">
         <v>38</v>
       </c>
@@ -1308,7 +1313,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="15.9">
       <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
@@ -1316,7 +1321,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="15.9">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -1324,7 +1329,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15.9">
       <c r="A40" s="9" t="s">
         <v>80</v>
       </c>
@@ -1332,7 +1337,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15.9">
       <c r="A41" s="9" t="s">
         <v>81</v>
       </c>
@@ -1340,7 +1345,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="15.9">
       <c r="A42" s="9" t="s">
         <v>82</v>
       </c>
@@ -1348,7 +1353,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="15.9">
       <c r="A43" s="9" t="s">
         <v>83</v>
       </c>
